--- a/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
+++ b/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCharacter" sheetId="1" r:id="Re5f6e09432d74e3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCharacter" sheetId="1" r:id="R14a90c86f1414ed9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,35 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="等线"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="等线"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -93,6 +120,41 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF64748B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6F8FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -180,7 +242,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -290,6 +352,57 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -497,6 +610,14 @@
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="29" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="29" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="29" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="29" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -512,6 +633,30 @@
       <x:c r="D1" s="11" t="str">
         <x:v>visualSetId</x:v>
       </x:c>
+      <x:c r="E1" s="43" t="str">
+        <x:v>attributeProfileId</x:v>
+      </x:c>
+      <x:c r="F1" s="43" t="str">
+        <x:v>defaultSkillId</x:v>
+      </x:c>
+      <x:c r="G1" s="43" t="str">
+        <x:v>bodyRadius</x:v>
+      </x:c>
+      <x:c r="H1" s="52" t="str">
+        <x:v>moveRadiusPixels</x:v>
+      </x:c>
+      <x:c r="I1" s="52" t="str">
+        <x:v>moveHeightPixels</x:v>
+      </x:c>
+      <x:c r="J1" s="52" t="str">
+        <x:v>moveOffsetXPixels</x:v>
+      </x:c>
+      <x:c r="K1" s="52" t="str">
+        <x:v>moveOffsetYPixels</x:v>
+      </x:c>
+      <x:c r="L1" s="52" t="str">
+        <x:v>moveElevationPixels</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
@@ -526,6 +671,30 @@
       <x:c r="D2" s="14" t="str">
         <x:v>int#ref=TbVisualSet</x:v>
       </x:c>
+      <x:c r="E2" s="45" t="str">
+        <x:v>int?#ref=TbAttributeProfile</x:v>
+      </x:c>
+      <x:c r="F2" s="45" t="str">
+        <x:v>int?#ref=TbSkill</x:v>
+      </x:c>
+      <x:c r="G2" s="45" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="H2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="I2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="J2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="K2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="L2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="30" t="str">
@@ -534,8 +703,16 @@
       <x:c r="B3" s="16"/>
       <x:c r="C3" s="16"/>
       <x:c r="D3" s="16"/>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="E3" s="46"/>
+      <x:c r="F3" s="46"/>
+      <x:c r="G3" s="46"/>
+      <x:c r="H3" s="50"/>
+      <x:c r="I3" s="50"/>
+      <x:c r="J3" s="50"/>
+      <x:c r="K3" s="50"/>
+      <x:c r="L3" s="50"/>
+    </x:row>
+    <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>##</x:v>
       </x:c>
@@ -547,6 +724,30 @@
       </x:c>
       <x:c r="D4" s="24" t="str">
         <x:v>角色表现集合ID</x:v>
+      </x:c>
+      <x:c r="E4" s="47" t="str">
+        <x:v>战斗属性方案；空值仅可预览</x:v>
+      </x:c>
+      <x:c r="F4" s="47" t="str">
+        <x:v>默认装备技能；不同于已解锁技能</x:v>
+      </x:c>
+      <x:c r="G4" s="47" t="str">
+        <x:v>伤害判定身体半径，世界单位；独立于移动圆柱</x:v>
+      </x:c>
+      <x:c r="H4" s="54" t="str">
+        <x:v>移动圆柱半径，逻辑像素；由预制体导出</x:v>
+      </x:c>
+      <x:c r="I4" s="54" t="str">
+        <x:v>移动圆柱高度，逻辑像素；由预制体导出</x:v>
+      </x:c>
+      <x:c r="J4" s="54" t="str">
+        <x:v>圆柱底心横向偏移，逻辑像素</x:v>
+      </x:c>
+      <x:c r="K4" s="54" t="str">
+        <x:v>圆柱底心地面纵向偏移，逻辑像素</x:v>
+      </x:c>
+      <x:c r="L4" s="54" t="str">
+        <x:v>圆柱底面离地高度，逻辑像素</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -560,354 +761,516 @@
       <x:c r="D5" s="35" t="n">
         <x:v>10001</x:v>
       </x:c>
+      <x:c r="E5" s="41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="41" t="n">
+        <x:v>20001</x:v>
+      </x:c>
+      <x:c r="G5" s="41" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H5" s="50">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I5" s="50">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J5" s="50">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="50">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="50">
+        <x:v>1.99999809</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33"/>
       <x:c r="B6" s="36" t="n">
-        <x:v>10002</x:v>
+        <x:v>10006</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
-        <x:v>B_1_d</x:v>
+        <x:v>H_0</x:v>
       </x:c>
       <x:c r="D6" s="36" t="n">
-        <x:v>10002</x:v>
+        <x:v>10007</x:v>
+      </x:c>
+      <x:c r="E6" s="41"/>
+      <x:c r="F6" s="41"/>
+      <x:c r="G6" s="41"/>
+      <x:c r="H6">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I6">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J6">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6">
+        <x:v>-8.499998</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="33"/>
       <x:c r="B7" s="36" t="n">
-        <x:v>10003</x:v>
+        <x:v>10011</x:v>
       </x:c>
       <x:c r="C7" s="33" t="str">
-        <x:v>B_2_d</x:v>
+        <x:v>J_0</x:v>
       </x:c>
       <x:c r="D7" s="36" t="n">
-        <x:v>10003</x:v>
+        <x:v>10012</x:v>
+      </x:c>
+      <x:c r="E7" s="41"/>
+      <x:c r="F7" s="41"/>
+      <x:c r="G7" s="41"/>
+      <x:c r="H7">
+        <x:v>46.5</x:v>
+      </x:c>
+      <x:c r="I7">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="J7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7">
+        <x:v>-0.499999523</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33"/>
       <x:c r="B8" s="36" t="n">
-        <x:v>10004</x:v>
+        <x:v>10016</x:v>
       </x:c>
       <x:c r="C8" s="33" t="str">
-        <x:v>B_3_d</x:v>
+        <x:v>K_0</x:v>
       </x:c>
       <x:c r="D8" s="36" t="n">
-        <x:v>10004</x:v>
+        <x:v>10017</x:v>
+      </x:c>
+      <x:c r="E8" s="41"/>
+      <x:c r="F8" s="41"/>
+      <x:c r="G8" s="41"/>
+      <x:c r="H8">
+        <x:v>36.5</x:v>
+      </x:c>
+      <x:c r="I8">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="J8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8">
+        <x:v>-13.2999964</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33"/>
       <x:c r="B9" s="36" t="n">
-        <x:v>10005</x:v>
+        <x:v>10021</x:v>
       </x:c>
       <x:c r="C9" s="33" t="str">
-        <x:v>B_4_d</x:v>
+        <x:v>Y_0</x:v>
       </x:c>
       <x:c r="D9" s="36" t="n">
-        <x:v>10005</x:v>
+        <x:v>10022</x:v>
+      </x:c>
+      <x:c r="E9" s="41"/>
+      <x:c r="F9" s="41"/>
+      <x:c r="G9" s="41"/>
+      <x:c r="H9">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I9">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J9">
+        <x:v>-10.7000008</x:v>
+      </x:c>
+      <x:c r="K9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9">
+        <x:v>-15.699995</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33"/>
       <x:c r="B10" s="36" t="n">
-        <x:v>10006</x:v>
+        <x:v>10026</x:v>
       </x:c>
       <x:c r="C10" s="33" t="str">
-        <x:v>H_0</x:v>
+        <x:v>Z_0</x:v>
       </x:c>
       <x:c r="D10" s="36" t="n">
-        <x:v>10007</x:v>
+        <x:v>10027</x:v>
+      </x:c>
+      <x:c r="E10" s="41"/>
+      <x:c r="F10" s="41"/>
+      <x:c r="G10" s="41"/>
+      <x:c r="H10">
+        <x:v>46.9999962</x:v>
+      </x:c>
+      <x:c r="I10">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10">
+        <x:v>-8.700002</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33"/>
-      <x:c r="B11" s="36" t="n">
-        <x:v>10007</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>H_1_d</x:v>
-      </x:c>
-      <x:c r="D11" s="36" t="n">
-        <x:v>10008</x:v>
-      </x:c>
+      <x:c r="B11" s="36"/>
+      <x:c r="C11" s="33"/>
+      <x:c r="D11" s="36"/>
+      <x:c r="E11" s="41"/>
+      <x:c r="F11" s="41"/>
+      <x:c r="G11" s="41"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33"/>
-      <x:c r="B12" s="36" t="n">
-        <x:v>10008</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>H_2_d</x:v>
-      </x:c>
-      <x:c r="D12" s="36" t="n">
-        <x:v>10009</x:v>
-      </x:c>
+      <x:c r="B12" s="36"/>
+      <x:c r="C12" s="33"/>
+      <x:c r="D12" s="36"/>
+      <x:c r="E12" s="41"/>
+      <x:c r="F12" s="41"/>
+      <x:c r="G12" s="41"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33"/>
-      <x:c r="B13" s="36" t="n">
-        <x:v>10009</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>H_3_d</x:v>
-      </x:c>
-      <x:c r="D13" s="36" t="n">
-        <x:v>10010</x:v>
-      </x:c>
+      <x:c r="B13" s="36"/>
+      <x:c r="C13" s="33"/>
+      <x:c r="D13" s="36"/>
+      <x:c r="E13" s="41"/>
+      <x:c r="F13" s="41"/>
+      <x:c r="G13" s="41"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33"/>
-      <x:c r="B14" s="36" t="n">
-        <x:v>10010</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="str">
-        <x:v>H_4_d</x:v>
-      </x:c>
-      <x:c r="D14" s="36" t="n">
-        <x:v>10011</x:v>
-      </x:c>
+      <x:c r="B14" s="36"/>
+      <x:c r="C14" s="33"/>
+      <x:c r="D14" s="36"/>
+      <x:c r="E14" s="41"/>
+      <x:c r="F14" s="41"/>
+      <x:c r="G14" s="41"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33"/>
-      <x:c r="B15" s="36" t="n">
-        <x:v>10011</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="str">
-        <x:v>J_0</x:v>
-      </x:c>
-      <x:c r="D15" s="36" t="n">
-        <x:v>10012</x:v>
-      </x:c>
+      <x:c r="B15" s="36"/>
+      <x:c r="C15" s="33"/>
+      <x:c r="D15" s="36"/>
+      <x:c r="E15" s="41"/>
+      <x:c r="F15" s="41"/>
+      <x:c r="G15" s="41"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33"/>
-      <x:c r="B16" s="36" t="n">
-        <x:v>10012</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="str">
-        <x:v>J_1_d</x:v>
-      </x:c>
-      <x:c r="D16" s="36" t="n">
-        <x:v>10013</x:v>
-      </x:c>
+      <x:c r="B16" s="36"/>
+      <x:c r="C16" s="33"/>
+      <x:c r="D16" s="36"/>
+      <x:c r="E16" s="41"/>
+      <x:c r="F16" s="41"/>
+      <x:c r="G16" s="41"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33"/>
-      <x:c r="B17" s="36" t="n">
-        <x:v>10013</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="str">
-        <x:v>J_2_d</x:v>
-      </x:c>
-      <x:c r="D17" s="36" t="n">
-        <x:v>10014</x:v>
-      </x:c>
+      <x:c r="B17" s="36"/>
+      <x:c r="C17" s="33"/>
+      <x:c r="D17" s="36"/>
+      <x:c r="E17" s="41"/>
+      <x:c r="F17" s="41"/>
+      <x:c r="G17" s="41"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="33"/>
-      <x:c r="B18" s="36" t="n">
-        <x:v>10014</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="str">
-        <x:v>J_3_d</x:v>
-      </x:c>
-      <x:c r="D18" s="36" t="n">
-        <x:v>10015</x:v>
-      </x:c>
+      <x:c r="B18" s="36"/>
+      <x:c r="C18" s="33"/>
+      <x:c r="D18" s="36"/>
+      <x:c r="E18" s="41"/>
+      <x:c r="F18" s="41"/>
+      <x:c r="G18" s="41"/>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="33"/>
-      <x:c r="B19" s="36" t="n">
-        <x:v>10015</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="str">
-        <x:v>J_4_d</x:v>
-      </x:c>
-      <x:c r="D19" s="36" t="n">
-        <x:v>10016</x:v>
-      </x:c>
+      <x:c r="B19" s="36"/>
+      <x:c r="C19" s="33"/>
+      <x:c r="D19" s="36"/>
+      <x:c r="E19" s="41"/>
+      <x:c r="F19" s="41"/>
+      <x:c r="G19" s="41"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="33"/>
-      <x:c r="B20" s="36" t="n">
-        <x:v>10016</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="str">
-        <x:v>K_0</x:v>
-      </x:c>
-      <x:c r="D20" s="36" t="n">
-        <x:v>10017</x:v>
-      </x:c>
+      <x:c r="B20" s="36"/>
+      <x:c r="C20" s="33"/>
+      <x:c r="D20" s="36"/>
+      <x:c r="E20" s="41"/>
+      <x:c r="F20" s="41"/>
+      <x:c r="G20" s="41"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="33"/>
-      <x:c r="B21" s="36" t="n">
-        <x:v>10017</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="str">
-        <x:v>K_1_d</x:v>
-      </x:c>
-      <x:c r="D21" s="36" t="n">
-        <x:v>10018</x:v>
-      </x:c>
+      <x:c r="B21" s="36"/>
+      <x:c r="C21" s="33"/>
+      <x:c r="D21" s="36"/>
+      <x:c r="E21" s="41"/>
+      <x:c r="F21" s="41"/>
+      <x:c r="G21" s="41"/>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="33"/>
-      <x:c r="B22" s="36" t="n">
-        <x:v>10018</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="str">
-        <x:v>K_2_d</x:v>
-      </x:c>
-      <x:c r="D22" s="36" t="n">
-        <x:v>10019</x:v>
-      </x:c>
+      <x:c r="B22" s="36"/>
+      <x:c r="C22" s="33"/>
+      <x:c r="D22" s="36"/>
+      <x:c r="E22" s="41"/>
+      <x:c r="F22" s="41"/>
+      <x:c r="G22" s="41"/>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="33"/>
-      <x:c r="B23" s="36" t="n">
-        <x:v>10019</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="str">
-        <x:v>K_3_d</x:v>
-      </x:c>
-      <x:c r="D23" s="36" t="n">
-        <x:v>10020</x:v>
-      </x:c>
+      <x:c r="B23" s="36"/>
+      <x:c r="C23" s="33"/>
+      <x:c r="D23" s="36"/>
+      <x:c r="E23" s="41"/>
+      <x:c r="F23" s="41"/>
+      <x:c r="G23" s="41"/>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="33"/>
-      <x:c r="B24" s="36" t="n">
-        <x:v>10020</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="str">
-        <x:v>K_4_d</x:v>
-      </x:c>
-      <x:c r="D24" s="36" t="n">
-        <x:v>10021</x:v>
-      </x:c>
+      <x:c r="B24" s="36"/>
+      <x:c r="C24" s="33"/>
+      <x:c r="D24" s="36"/>
+      <x:c r="E24" s="41"/>
+      <x:c r="F24" s="41"/>
+      <x:c r="G24" s="41"/>
+      <x:c r="H24"/>
+      <x:c r="I24"/>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="33"/>
-      <x:c r="B25" s="36" t="n">
-        <x:v>10021</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="str">
-        <x:v>Y_0</x:v>
-      </x:c>
-      <x:c r="D25" s="36" t="n">
-        <x:v>10022</x:v>
-      </x:c>
+      <x:c r="B25" s="36"/>
+      <x:c r="C25" s="33"/>
+      <x:c r="D25" s="36"/>
+      <x:c r="E25" s="41"/>
+      <x:c r="F25" s="41"/>
+      <x:c r="G25" s="41"/>
+      <x:c r="H25"/>
+      <x:c r="I25"/>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="33"/>
-      <x:c r="B26" s="36" t="n">
-        <x:v>10022</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="str">
-        <x:v>Y_1_d</x:v>
-      </x:c>
-      <x:c r="D26" s="36" t="n">
-        <x:v>10023</x:v>
-      </x:c>
+      <x:c r="B26" s="36"/>
+      <x:c r="C26" s="33"/>
+      <x:c r="D26" s="36"/>
+      <x:c r="E26" s="41"/>
+      <x:c r="F26" s="41"/>
+      <x:c r="G26" s="41"/>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="33"/>
-      <x:c r="B27" s="36" t="n">
-        <x:v>10023</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="str">
-        <x:v>Y_2_d</x:v>
-      </x:c>
-      <x:c r="D27" s="36" t="n">
-        <x:v>10024</x:v>
-      </x:c>
+      <x:c r="B27" s="36"/>
+      <x:c r="C27" s="33"/>
+      <x:c r="D27" s="36"/>
+      <x:c r="E27" s="41"/>
+      <x:c r="F27" s="41"/>
+      <x:c r="G27" s="41"/>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="33"/>
-      <x:c r="B28" s="36" t="n">
-        <x:v>10024</x:v>
-      </x:c>
-      <x:c r="C28" s="33" t="str">
-        <x:v>Y_3_d</x:v>
-      </x:c>
-      <x:c r="D28" s="36" t="n">
-        <x:v>10025</x:v>
-      </x:c>
+      <x:c r="B28" s="36"/>
+      <x:c r="C28" s="33"/>
+      <x:c r="D28" s="36"/>
+      <x:c r="E28" s="41"/>
+      <x:c r="F28" s="41"/>
+      <x:c r="G28" s="41"/>
+      <x:c r="H28"/>
+      <x:c r="I28"/>
+      <x:c r="J28"/>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="33"/>
-      <x:c r="B29" s="36" t="n">
-        <x:v>10025</x:v>
-      </x:c>
-      <x:c r="C29" s="33" t="str">
-        <x:v>Y_4_d</x:v>
-      </x:c>
-      <x:c r="D29" s="36" t="n">
-        <x:v>10026</x:v>
-      </x:c>
+      <x:c r="B29" s="36"/>
+      <x:c r="C29" s="33"/>
+      <x:c r="D29" s="36"/>
+      <x:c r="E29" s="41"/>
+      <x:c r="F29" s="41"/>
+      <x:c r="G29" s="41"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="33"/>
-      <x:c r="B30" s="36" t="n">
-        <x:v>10026</x:v>
-      </x:c>
-      <x:c r="C30" s="33" t="str">
-        <x:v>Z_0</x:v>
-      </x:c>
-      <x:c r="D30" s="36" t="n">
-        <x:v>10027</x:v>
-      </x:c>
+      <x:c r="B30" s="36"/>
+      <x:c r="C30" s="33"/>
+      <x:c r="D30" s="36"/>
+      <x:c r="E30" s="41"/>
+      <x:c r="F30" s="41"/>
+      <x:c r="G30" s="41"/>
+      <x:c r="H30"/>
+      <x:c r="I30"/>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="33"/>
-      <x:c r="B31" s="36" t="n">
-        <x:v>10027</x:v>
-      </x:c>
-      <x:c r="C31" s="33" t="str">
-        <x:v>Z_1_d</x:v>
-      </x:c>
-      <x:c r="D31" s="36" t="n">
-        <x:v>10028</x:v>
-      </x:c>
+      <x:c r="B31" s="36"/>
+      <x:c r="C31" s="33"/>
+      <x:c r="D31" s="36"/>
+      <x:c r="E31" s="41"/>
+      <x:c r="F31" s="41"/>
+      <x:c r="G31" s="41"/>
+      <x:c r="H31"/>
+      <x:c r="I31"/>
+      <x:c r="J31"/>
+      <x:c r="K31"/>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="33"/>
-      <x:c r="B32" s="36" t="n">
-        <x:v>10028</x:v>
-      </x:c>
-      <x:c r="C32" s="33" t="str">
-        <x:v>Z_2_d</x:v>
-      </x:c>
-      <x:c r="D32" s="36" t="n">
-        <x:v>10029</x:v>
-      </x:c>
+      <x:c r="B32" s="36"/>
+      <x:c r="C32" s="33"/>
+      <x:c r="D32" s="36"/>
+      <x:c r="E32" s="41"/>
+      <x:c r="F32" s="41"/>
+      <x:c r="G32" s="41"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="33"/>
-      <x:c r="B33" s="36" t="n">
-        <x:v>10029</x:v>
-      </x:c>
-      <x:c r="C33" s="33" t="str">
-        <x:v>Z_3_d</x:v>
-      </x:c>
-      <x:c r="D33" s="36" t="n">
-        <x:v>10030</x:v>
-      </x:c>
+      <x:c r="B33" s="36"/>
+      <x:c r="C33" s="33"/>
+      <x:c r="D33" s="36"/>
+      <x:c r="E33" s="41"/>
+      <x:c r="F33" s="41"/>
+      <x:c r="G33" s="41"/>
+      <x:c r="H33"/>
+      <x:c r="I33"/>
+      <x:c r="J33"/>
+      <x:c r="K33"/>
+      <x:c r="L33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="34"/>
-      <x:c r="B34" s="37" t="n">
-        <x:v>10030</x:v>
-      </x:c>
-      <x:c r="C34" s="34" t="str">
-        <x:v>Z_4_d</x:v>
-      </x:c>
-      <x:c r="D34" s="37" t="n">
-        <x:v>10031</x:v>
-      </x:c>
+      <x:c r="B34" s="37"/>
+      <x:c r="C34" s="34"/>
+      <x:c r="D34" s="37"/>
+      <x:c r="E34" s="41"/>
+      <x:c r="F34" s="41"/>
+      <x:c r="G34" s="41"/>
+      <x:c r="H34"/>
+      <x:c r="I34"/>
+      <x:c r="J34"/>
+      <x:c r="K34"/>
+      <x:c r="L34"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
+++ b/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
@@ -1,399 +1,260 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Roguelike\Config\Datas\Tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24750" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TbCharacter" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCharacter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>visualSetId</t>
-  </si>
-  <si>
-    <t>attributeProfileId</t>
-  </si>
-  <si>
-    <t>defaultSkillId</t>
-  </si>
-  <si>
-    <t>bodyRadiusMilli</t>
-  </si>
-  <si>
-    <t>moveRadiusPixelsMilli</t>
-  </si>
-  <si>
-    <t>moveHeightPixelsMilli</t>
-  </si>
-  <si>
-    <t>moveOffsetXPixelsMilli</t>
-  </si>
-  <si>
-    <t>moveOffsetYPixelsMilli</t>
-  </si>
-  <si>
-    <t>moveElevationPixelsMilli</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int#ref=TbVisualSet</t>
-  </si>
-  <si>
-    <t>int?#ref=TbAttributeProfile</t>
-  </si>
-  <si>
-    <t>int?#ref=TbSkill</t>
-  </si>
-  <si>
-    <t>int?</t>
-  </si>
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>角色ID：从10001开始递增</t>
-  </si>
-  <si>
-    <t>临时显示名，当前使用资源前缀</t>
-  </si>
-  <si>
-    <t>角色表现集合ID</t>
-  </si>
-  <si>
-    <t>战斗属性方案；空值仅可预览</t>
-  </si>
-  <si>
-    <t>默认装备技能；不同于已解锁技能</t>
-  </si>
-  <si>
-    <t>伤害判定身体半径，世界单位；独立于移动圆柱；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-  </si>
-  <si>
-    <t>移动圆柱半径，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-  </si>
-  <si>
-    <t>移动圆柱高度，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-  </si>
-  <si>
-    <t>圆柱底心横向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-  </si>
-  <si>
-    <t>圆柱底心地面纵向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-  </si>
-  <si>
-    <t>圆柱底面离地高度，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
-  </si>
-  <si>
-    <t>B_0</t>
-  </si>
-  <si>
-    <t>H_0</t>
-  </si>
-  <si>
-    <t>J_0</t>
-  </si>
-  <si>
-    <t>K_0</t>
-  </si>
-  <si>
-    <t>Y_0</t>
-  </si>
-  <si>
-    <t>Z_0</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="33">
     <font>
-      <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FF17324D"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="FF17324D"/>
       <sz val="10"/>
-      <color rgb="FF17365D"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FF17365D"/>
       <sz val="10"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF52606D"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <i val="1"/>
+      <color rgb="FF52606D"/>
       <sz val="10"/>
-      <color rgb="FF334155"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF334155"/>
       <sz val="10"/>
-      <color rgb="FF475569"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF475569"/>
       <sz val="10"/>
-      <color rgb="FF1F2937"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF1F2937"/>
       <sz val="10"/>
-      <color rgb="FF1F2937"/>
+    </font>
+    <font>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF334155"/>
+      <color rgb="FF1F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF334155"/>
       <sz val="11"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="41">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -811,232 +672,233 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="6" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1283,7 +1145,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1292,7 +1154,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1305,11 +1167,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1506,553 +1431,674 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="7" width="24" customWidth="1"/>
-    <col min="8" max="12" width="29" customWidth="1"/>
+    <col width="12" customWidth="1" style="26" min="1" max="1"/>
+    <col width="16" customWidth="1" style="26" min="2" max="2"/>
+    <col width="24" customWidth="1" style="26" min="3" max="3"/>
+    <col width="20" customWidth="1" style="26" min="4" max="4"/>
+    <col width="24" customWidth="1" style="26" min="5" max="7"/>
+    <col width="29" customWidth="1" style="26" min="8" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="30" customHeight="1" s="26">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>visualSetId</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>attributeProfileId</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>defaultSkillId</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>bodyRadiusMilli</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>moveRadiusPixelsMilli</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>moveHeightPixelsMilli</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>moveOffsetXPixelsMilli</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>moveOffsetYPixelsMilli</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>moveElevationPixelsMilli</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>damageFloatHeight</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="26">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>int#ref=TbVisualSet</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>int?#ref=TbAttributeProfile</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>int?#ref=TbSkill</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="26">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+    </row>
+    <row r="4" ht="70" customHeight="1" s="26">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>角色ID：从10001开始递增</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>临时显示名，当前使用资源前缀</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>角色表现集合ID</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>战斗属性方案；空值仅可预览</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>默认装备技能；不同于已解锁技能</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>伤害判定身体半径，世界单位；独立于移动圆柱；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>移动圆柱半径，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>移动圆柱高度，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>圆柱底心横向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>圆柱底心地面纵向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>圆柱底面离地高度，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>掉血/伤害数字浮动锚点高度（世界单位，Y轴向上）；由预制体 DamageFloatAnchor 节点 localPosition.y 导出；运行时叠加到单位世界坐标上方定位伤害数字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="16" t="n">
+        <v>10001</v>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>B_0</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>20001</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>31000</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" ht="70" customHeight="1" spans="1:12">
-      <c r="A4" s="11" t="s">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="16">
-        <v>10001</v>
-      </c>
-      <c r="E5" s="18">
-        <v>1</v>
-      </c>
-      <c r="F5" s="18">
-        <v>20001</v>
-      </c>
-      <c r="G5" s="18">
-        <v>200</v>
-      </c>
-      <c r="H5" s="10">
-        <v>31000</v>
-      </c>
-      <c r="I5" s="10">
-        <v>150000</v>
-      </c>
-      <c r="J5" s="10">
+      <c r="L5" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="16" t="n">
+        <v>10006</v>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>H_0</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>10007</v>
+      </c>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="10">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="19"/>
-      <c r="B6" s="16">
-        <v>10006</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="16">
-        <v>10007</v>
-      </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="20">
-        <v>40000</v>
-      </c>
-      <c r="I6" s="20">
-        <v>154000</v>
-      </c>
-      <c r="J6" s="20">
+      <c r="L6" s="20" t="n">
+        <v>-8500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="16" t="n">
+        <v>10011</v>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>J_0</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>10012</v>
+      </c>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="20" t="n">
+        <v>46500</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>152000</v>
+      </c>
+      <c r="J7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="20">
-        <v>-8500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="19"/>
-      <c r="B7" s="16">
-        <v>10011</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="16">
-        <v>10012</v>
-      </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="20">
-        <v>46500</v>
-      </c>
-      <c r="I7" s="20">
-        <v>152000</v>
-      </c>
-      <c r="J7" s="20">
+      <c r="L7" s="20" t="n">
+        <v>-500</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="16" t="n">
+        <v>10016</v>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>K_0</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>10017</v>
+      </c>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="20" t="n">
+        <v>36500</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>153000</v>
+      </c>
+      <c r="J8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="20">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="19"/>
-      <c r="B8" s="16">
-        <v>10016</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="16">
-        <v>10017</v>
-      </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="20">
-        <v>36500</v>
-      </c>
-      <c r="I8" s="20">
-        <v>153000</v>
-      </c>
-      <c r="J8" s="20">
+      <c r="L8" s="20" t="n">
+        <v>-13300</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="16" t="n">
+        <v>10021</v>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Y_0</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>10022</v>
+      </c>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="20" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>145000</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>-10700</v>
+      </c>
+      <c r="K9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="20">
+      <c r="L9" s="20" t="n">
+        <v>-15700</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="16" t="n">
+        <v>10026</v>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Z_0</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>10027</v>
+      </c>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="20" t="n">
+        <v>47000</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>148000</v>
+      </c>
+      <c r="J10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="20">
-        <v>-13300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="19"/>
-      <c r="B9" s="16">
-        <v>10021</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="16">
-        <v>10022</v>
-      </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="20">
-        <v>45000</v>
-      </c>
-      <c r="I9" s="20">
-        <v>145000</v>
-      </c>
-      <c r="J9" s="20">
-        <v>-10700</v>
-      </c>
-      <c r="K9" s="20">
+      <c r="K10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="20">
-        <v>-15700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="19"/>
-      <c r="B10" s="16">
-        <v>10026</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="16">
-        <v>10027</v>
-      </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="20">
-        <v>47000</v>
-      </c>
-      <c r="I10" s="20">
-        <v>148000</v>
-      </c>
-      <c r="J10" s="20">
-        <v>0</v>
-      </c>
-      <c r="K10" s="20">
-        <v>0</v>
-      </c>
-      <c r="L10" s="20">
+      <c r="L10" s="20" t="n">
         <v>-8700</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:12">
-      <c r="A11" s="19"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:12">
-      <c r="A12" s="19"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:12">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:12">
-      <c r="A14" s="19"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:12">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:12">
-      <c r="A16" s="19"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:7">
-      <c r="A18" s="19"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:7">
-      <c r="A19" s="19"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:7">
-      <c r="A20" s="19"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:7">
-      <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:7">
-      <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:7">
-      <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:7">
-      <c r="A24" s="19"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:7">
-      <c r="A25" s="19"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:7">
-      <c r="A26" s="19"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:7">
-      <c r="A27" s="19"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:7">
-      <c r="A28" s="19"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:7">
-      <c r="A29" s="19"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:7">
-      <c r="A30" s="19"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:7">
-      <c r="A31" s="19"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:7">
-      <c r="A32" s="19"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:7">
-      <c r="A33" s="19"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:7">
-      <c r="A34" s="24"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
+      <c r="M10" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="26">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" s="26">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" s="26">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="26">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" s="26">
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" s="26">
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="26">
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="26">
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="26">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" s="26">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="26">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="26">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="26">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="26">
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="26">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="26">
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="26">
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="26">
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="26">
+      <c r="A29" s="19" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="26">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" s="26">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" s="26">
+      <c r="A32" s="19" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" s="26">
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="26">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
+++ b/Config/Datas/Tables/j_角色_CharacterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCharacter" sheetId="1" r:id="R18f23973f95b4a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCharacter" sheetId="1" r:id="Rf80a140955b042a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1300,52 +1300,40 @@
         </x:is>
       </x:c>
       <x:c r="G1" s="2" t="str">
-        <x:v>bodyRadiusPixelsMilli</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">moveRadiusPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">moveHeightPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">moveOffsetXPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">moveOffsetYPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">moveElevationPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">damageFloatHeight</x:t>
-        </x:is>
+        <x:v>bodyRadiusPixels</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="str">
+        <x:v>moveRadiusPixels</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="str">
+        <x:v>moveHeightPixels</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="str">
+        <x:v>moveOffsetXPixels</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="str">
+        <x:v>moveOffsetYPixels</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="str">
+        <x:v>moveElevationPixels</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>damageFloatHeightPixels</x:v>
       </x:c>
       <x:c r="N1" t="str">
-        <x:v>bodyOffsetXPixelsMilli</x:v>
+        <x:v>bodyOffsetXPixels</x:v>
       </x:c>
       <x:c r="O1" t="str">
-        <x:v>bodyOffsetYPixelsMilli</x:v>
+        <x:v>bodyOffsetYPixels</x:v>
       </x:c>
       <x:c r="P1" t="str">
         <x:v>collisionShape</x:v>
       </x:c>
       <x:c r="Q1" t="str">
-        <x:v>hitEffectOffsetXPixelsMilli</x:v>
+        <x:v>hitEffectOffsetXPixels</x:v>
       </x:c>
       <x:c r="R1" t="str">
-        <x:v>hitEffectOffsetYPixelsMilli</x:v>
+        <x:v>hitEffectOffsetYPixels</x:v>
       </x:c>
     </x:row>
     <x:row r="2" s="26" customFormat="1" ht="30" customHeight="1">
@@ -1379,55 +1367,41 @@
           <x:t xml:space="preserve">int?#ref=TbSkill</x:t>
         </x:is>
       </x:c>
-      <x:c r="G2" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K2" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L2" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float?</x:t>
-        </x:is>
+      <x:c r="G2" s="5" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="N2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="P2" t="str">
         <x:v>EUnitCollisionShape?</x:v>
       </x:c>
       <x:c r="Q2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="R2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
     </x:row>
     <x:row r="3" s="26" customFormat="1" ht="30" customHeight="1">
@@ -1485,52 +1459,40 @@
         </x:is>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>受击判定半径（像素）；由角色预制体“受击判定范围”节点导出；像素值×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
-      </x:c>
-      <x:c r="H4" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">移动圆柱半径，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">移动圆柱高度，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J4" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆柱底心横向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K4" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆柱底心地面纵向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L4" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆柱底面离地高度，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">掉血/伤害数字浮动锚点高度（世界单位，Y轴向上）；由预制体 DamageFloatAnchor 节点 localPosition.y 导出；运行时叠加到单位世界坐标上方定位伤害数字。</x:t>
-        </x:is>
+        <x:v>受击判定半径；由角色预制体“受击判定范围”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>移动圆柱半径；由预制体导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>移动圆柱高度；由预制体导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>圆柱底心横向偏移，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>圆柱底心地面纵向偏移，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>圆柱底面离地高度，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>掉血/伤害数字浮动锚点高度；由预制体 DamageFloatAnchor 节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>受击判定中心横向偏移（像素）；由角色预制体“受击判定范围”节点导出；像素值×1000存整数。</x:v>
+        <x:v>受击判定中心横向偏移；由角色预制体“受击判定范围”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>受击判定中心前向偏移（像素）；由角色预制体“受击判定范围”节点导出；像素值×1000存整数。</x:v>
+        <x:v>受击判定中心前向偏移；由角色预制体“受击判定范围”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="P4" t="str">
         <x:v>统一碰撞形状；VerticalCapsule 表示移动阻挡与受击判定共用预制体 CapsuleCollider2D。</x:v>
       </x:c>
       <x:c r="Q4" t="str">
-        <x:v>命中特效挂点横向偏移（逻辑像素）；由角色预制体“命中特效挂点”节点 localPosition.x 导出；像素值×1000存整数。</x:v>
+        <x:v>命中特效挂点横向偏移；由角色预制体“命中特效挂点”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="R4" t="str">
-        <x:v>命中特效挂点纵向偏移（逻辑像素）；由角色预制体“命中特效挂点”节点 localPosition.y 导出；像素值×1000存整数。</x:v>
+        <x:v>命中特效挂点纵向偏移；由角色预制体“命中特效挂点”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1552,41 +1514,41 @@
       <x:c r="F5" s="18" t="n">
         <x:v>20001</x:v>
       </x:c>
-      <x:c r="G5" s="18">
-        <x:v>30815</x:v>
-      </x:c>
-      <x:c r="H5" s="10">
-        <x:v>30815</x:v>
-      </x:c>
-      <x:c r="I5" s="10">
-        <x:v>146522</x:v>
-      </x:c>
-      <x:c r="J5" s="10">
-        <x:v>485</x:v>
-      </x:c>
-      <x:c r="K5" s="10">
-        <x:v>72660</x:v>
-      </x:c>
-      <x:c r="L5" s="10">
+      <x:c r="G5" s="18" t="n">
+        <x:v>30.815</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="n">
+        <x:v>30.815</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="n">
+        <x:v>146.522</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="n">
+        <x:v>0.485</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="n">
+        <x:v>72.66</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M5" t="n">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="N5">
-        <x:v>485</x:v>
-      </x:c>
-      <x:c r="O5">
-        <x:v>72660</x:v>
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="N5" t="n">
+        <x:v>0.485</x:v>
+      </x:c>
+      <x:c r="O5" t="n">
+        <x:v>72.66</x:v>
       </x:c>
       <x:c r="P5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q5">
-        <x:v>485</x:v>
-      </x:c>
-      <x:c r="R5">
-        <x:v>72660</x:v>
+      <x:c r="Q5" t="n">
+        <x:v>0.485</x:v>
+      </x:c>
+      <x:c r="R5" t="n">
+        <x:v>72.66</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1604,41 +1566,41 @@
       </x:c>
       <x:c r="E6" s="18" t="n"/>
       <x:c r="F6" s="18" t="n"/>
-      <x:c r="H6" s="20">
-        <x:v>40000</x:v>
-      </x:c>
-      <x:c r="I6" s="20">
-        <x:v>154000</x:v>
-      </x:c>
-      <x:c r="J6" s="20">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="20">
-        <x:v>77000</x:v>
-      </x:c>
-      <x:c r="L6" s="20">
+      <x:c r="G6" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I6" s="20" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J6" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="L6" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" t="n">
-        <x:v>1.84</x:v>
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" t="n">
+        <x:v>77</x:v>
       </x:c>
       <x:c r="P6">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6">
-        <x:v>40000</x:v>
-      </x:c>
-      <x:c r="N6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O6">
-        <x:v>77000</x:v>
+      <x:c r="Q6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R6" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1656,41 +1618,41 @@
       </x:c>
       <x:c r="E7" s="18" t="n"/>
       <x:c r="F7" s="18" t="n"/>
-      <x:c r="H7" s="20">
-        <x:v>46500</x:v>
-      </x:c>
-      <x:c r="I7" s="20">
-        <x:v>152000</x:v>
-      </x:c>
-      <x:c r="J7" s="20">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="20">
-        <x:v>75500</x:v>
-      </x:c>
-      <x:c r="L7" s="20">
+      <x:c r="G7" t="n">
+        <x:v>46.5</x:v>
+      </x:c>
+      <x:c r="H7" s="20" t="n">
+        <x:v>46.5</x:v>
+      </x:c>
+      <x:c r="I7" s="20" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="J7" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>75.5</x:v>
+      </x:c>
+      <x:c r="L7" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M7" t="n">
-        <x:v>1.82</x:v>
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="N7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" t="n">
+        <x:v>75.5</x:v>
       </x:c>
       <x:c r="P7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7">
-        <x:v>46500</x:v>
-      </x:c>
-      <x:c r="N7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7">
-        <x:v>75500</x:v>
+      <x:c r="Q7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1708,41 +1670,41 @@
       </x:c>
       <x:c r="E8" s="18" t="n"/>
       <x:c r="F8" s="18" t="n"/>
-      <x:c r="H8" s="20">
-        <x:v>36500</x:v>
-      </x:c>
-      <x:c r="I8" s="20">
-        <x:v>153000</x:v>
-      </x:c>
-      <x:c r="J8" s="20">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="20">
-        <x:v>63200</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="G8" t="n">
+        <x:v>36.5</x:v>
+      </x:c>
+      <x:c r="H8" s="20" t="n">
+        <x:v>36.5</x:v>
+      </x:c>
+      <x:c r="I8" s="20" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="J8" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="20" t="n">
+        <x:v>63.2</x:v>
+      </x:c>
+      <x:c r="L8" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" t="n">
-        <x:v>1.83</x:v>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>63.2</x:v>
       </x:c>
       <x:c r="P8">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8">
-        <x:v>36500</x:v>
-      </x:c>
-      <x:c r="N8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O8">
-        <x:v>63200</x:v>
+      <x:c r="Q8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1760,41 +1722,41 @@
       </x:c>
       <x:c r="E9" s="18" t="n"/>
       <x:c r="F9" s="18" t="n"/>
-      <x:c r="H9" s="20">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="I9" s="20">
-        <x:v>145000</x:v>
-      </x:c>
-      <x:c r="J9" s="20">
-        <x:v>-10700</x:v>
-      </x:c>
-      <x:c r="K9" s="20">
-        <x:v>56800</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="G9" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H9" s="20" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I9" s="20" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J9" s="20" t="n">
+        <x:v>-10.7</x:v>
+      </x:c>
+      <x:c r="K9" s="20" t="n">
+        <x:v>56.8</x:v>
+      </x:c>
+      <x:c r="L9" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" t="n">
-        <x:v>1.75</x:v>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>-10.7</x:v>
+      </x:c>
+      <x:c r="O9" t="n">
+        <x:v>56.8</x:v>
       </x:c>
       <x:c r="P9">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="N9">
-        <x:v>-10700</x:v>
-      </x:c>
-      <x:c r="O9">
-        <x:v>56800</x:v>
+      <x:c r="Q9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1812,41 +1774,41 @@
       </x:c>
       <x:c r="E10" s="18" t="n"/>
       <x:c r="F10" s="18" t="n"/>
-      <x:c r="H10" s="20">
-        <x:v>47000</x:v>
-      </x:c>
-      <x:c r="I10" s="20">
-        <x:v>148000</x:v>
-      </x:c>
-      <x:c r="J10" s="20">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="20">
-        <x:v>65300</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="G10" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H10" s="20" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I10" s="20" t="n">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J10" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>65.3</x:v>
+      </x:c>
+      <x:c r="L10" s="20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M10" t="n">
-        <x:v>1.78</x:v>
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="N10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" t="n">
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="P10">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Q10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10">
-        <x:v>47000</x:v>
-      </x:c>
-      <x:c r="N10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10">
-        <x:v>65300</x:v>
+      <x:c r="Q10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="26" customFormat="1" ht="16.5" customHeight="1">
